--- a/R_Codes/DataSummary/Bacteria/Sample_Layer/Bacteria_Summary_Domain_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_Layer/Bacteria_Summary_Domain_by_Sample_Layer.xlsx
@@ -467,10 +467,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999994</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.493030011228702</v>
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.493275446679922</v>
       </c>
     </row>
   </sheetData>
@@ -509,7 +509,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.388377755041764</v>
+        <v>0.388677337037841</v>
       </c>
     </row>
   </sheetData>
@@ -584,10 +584,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999989</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.292502462393569</v>
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.292711215168049</v>
       </c>
     </row>
   </sheetData>
@@ -623,49 +623,49 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
+        <v>99.9999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.482853734146856</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.48251152385611</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100.000000000001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.500721752612892</v>
+        <v>0.501218559427867</v>
       </c>
     </row>
   </sheetData>
@@ -701,40 +701,118 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
+        <v>99.9999999999996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.324977020513115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.324493232087766</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>9</v>
+        <v>2.01072516992102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>99.9999999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.843743644554288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -743,76 +821,76 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>2.01072516992102</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>99.9999999999999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.842955372560756</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>11</v>
+        <v>2.87172268497805</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>99.9999999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.14676620597094</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -821,85 +899,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9001615492456</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.98423663300358</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.383747283360717</v>
+        <v>0.384129311117042</v>
       </c>
     </row>
   </sheetData>
